--- a/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="364">
   <si>
     <t>id</t>
   </si>
@@ -1593,6 +1593,18 @@
 Given that the question asks about the position of the telephone relative to the sofa and the power strip, we need to determine if the telephone is to the left, right, or back of the person standing by the sofa and facing the power strip.
 Since the telephone is not explicitly visible in any of the images, we need to use spatial reasoning to infer its location. The power strip is located near the whiteboard, and the sofa is near the whiteboard as well. The telephone is likely located in a location that is common for such objects in an office setting, such as on a desk or near a wall.
 Based on the spatial arrangement of the objects in the room, the telephone is likely to be to the left of the person standing by the sofa and facing the power strip. This is because the power strip is located near the whiteboard, and the telephone is likely to be located on a desk or near a wall, which is to the left of the sofa.
+Therefore, the answer is (C) C. left.
+&lt;answer&gt;C&lt;/answer&gt;</t>
+  </si>
+  <si>
+    <t>To answer the question, we need to determine the spatial relationship between the table, sofa, and fireplace based on the provided frames. The key is to establish the relative positions of these objects in the room.
+First, we need to identify the positions of the table and the sofa from the frames. The sofa is visible in one frame, and the table is visible in another. The fireplace is also visible in one of the frames.
+To determine the relative positions, we can use the following steps:
+1. Identify the positions of the table and sofa in the frames.
+2. Identify the position of the fireplace in the frames.
+3. Determine the relative positions of these objects based on the frames.
+From the frames, we can see that the table is on the left side of the room, and the sofa is on the right side of the room. The fireplace is on the left side of the room, near the wall.
+If I am standing by the table and facing the sofa, I would be facing the right side of the room. The fireplace is on the left side of the room, so it would be to my left.
 Therefore, the answer is (C) C. left.
 &lt;answer&gt;C&lt;/answer&gt;</t>
   </si>
@@ -5103,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>5.943430662155151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5132,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>14.93584775924683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5161,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>2.449634552001953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5190,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>2.390782594680786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5219,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>2.818069934844971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5248,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>2.444391250610352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5277,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>1.775380373001099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5306,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>4.19475793838501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5335,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>3.121698617935181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5364,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>1.259337902069092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5393,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>2.110971927642822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5422,7 +5434,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>1.92261004447937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5451,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>8.840114831924438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5480,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>3.156227111816406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5509,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>1.92644214630127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5538,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>6.244034290313721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5567,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>2.154091835021973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5596,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>2.307050943374634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5625,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>3.963453054428101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5642,7 +5654,7 @@
         <v>216</v>
       </c>
       <c r="E61" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="F61" t="s">
         <v>215</v>
@@ -5654,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>5.912117719650269</v>
+        <v>2.013509511947632</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5671,7 +5683,7 @@
         <v>217</v>
       </c>
       <c r="E62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F62" t="s">
         <v>215</v>
@@ -5683,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>2.736186265945435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5712,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>28.08139133453369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5729,7 +5741,7 @@
         <v>217</v>
       </c>
       <c r="E64" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F64" t="s">
         <v>217</v>
@@ -5741,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>4.074865341186523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5758,7 +5770,7 @@
         <v>215</v>
       </c>
       <c r="E65" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F65" t="s">
         <v>215</v>
@@ -5770,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>2.190788984298706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5787,7 +5799,7 @@
         <v>217</v>
       </c>
       <c r="E66" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F66" t="s">
         <v>216</v>
@@ -5799,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>2.743775844573975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5816,7 +5828,7 @@
         <v>217</v>
       </c>
       <c r="E67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F67" t="s">
         <v>216</v>
@@ -5828,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>2.348269701004028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5845,7 +5857,7 @@
         <v>218</v>
       </c>
       <c r="E68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F68" t="s">
         <v>218</v>
@@ -5857,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>3.012043237686157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5874,7 +5886,7 @@
         <v>217</v>
       </c>
       <c r="E69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F69" t="s">
         <v>217</v>
@@ -5886,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>2.867041349411011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5903,7 +5915,7 @@
         <v>216</v>
       </c>
       <c r="E70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F70" t="s">
         <v>218</v>
@@ -5915,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>3.115255355834961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5944,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>8.797203302383423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5961,7 +5973,7 @@
         <v>217</v>
       </c>
       <c r="E72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F72" t="s">
         <v>218</v>
@@ -5973,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>42.61602401733398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6002,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>22.08264374732971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6019,7 +6031,7 @@
         <v>217</v>
       </c>
       <c r="E74" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F74" t="s">
         <v>215</v>
@@ -6031,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>5.333327054977417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6060,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>6.324087142944336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6089,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>14.787348985672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6106,7 +6118,7 @@
         <v>216</v>
       </c>
       <c r="E77" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F77" t="s">
         <v>217</v>
@@ -6118,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>7.07513689994812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -6135,7 +6147,7 @@
         <v>216</v>
       </c>
       <c r="E78" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F78" t="s">
         <v>217</v>
@@ -6147,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>6.412630319595337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6176,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>10.57357573509216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6193,7 +6205,7 @@
         <v>215</v>
       </c>
       <c r="E80" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F80" t="s">
         <v>218</v>
@@ -6205,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>7.693625688552856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6222,7 +6234,7 @@
         <v>216</v>
       </c>
       <c r="E81" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F81" t="s">
         <v>216</v>
@@ -6234,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>7.286533117294312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6251,7 +6263,7 @@
         <v>217</v>
       </c>
       <c r="E82" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F82" t="s">
         <v>217</v>
@@ -6263,7 +6275,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>6.36825966835022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6280,7 +6292,7 @@
         <v>215</v>
       </c>
       <c r="E83" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F83" t="s">
         <v>215</v>
@@ -6292,7 +6304,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>5.201405763626099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6309,7 +6321,7 @@
         <v>216</v>
       </c>
       <c r="E84" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F84" t="s">
         <v>216</v>
@@ -6321,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>3.557626247406006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6350,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>6.931787490844727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6367,7 +6379,7 @@
         <v>215</v>
       </c>
       <c r="E86" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" t="s">
         <v>215</v>
@@ -6379,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <v>6.73103666305542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6396,7 +6408,7 @@
         <v>217</v>
       </c>
       <c r="E87" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F87" t="s">
         <v>215</v>
@@ -6408,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>12.89632344245911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6425,7 +6437,7 @@
         <v>215</v>
       </c>
       <c r="E88" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F88" t="s">
         <v>215</v>
@@ -6437,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>6.331032037734985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6454,7 +6466,7 @@
         <v>217</v>
       </c>
       <c r="E89" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F89" t="s">
         <v>217</v>
@@ -6466,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>5.827206134796143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6495,7 +6507,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>100.2873070240021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6512,7 +6524,7 @@
         <v>217</v>
       </c>
       <c r="E91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F91" t="s">
         <v>215</v>
@@ -6524,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>5.502602338790894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6553,7 +6565,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>15.93896532058716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6570,7 +6582,7 @@
         <v>216</v>
       </c>
       <c r="E93" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F93" t="s">
         <v>216</v>
@@ -6582,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>5.037154912948608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6599,7 +6611,7 @@
         <v>217</v>
       </c>
       <c r="E94" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F94" t="s">
         <v>215</v>
@@ -6611,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>6.756111860275269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6640,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>8.273808479309082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6657,7 +6669,7 @@
         <v>218</v>
       </c>
       <c r="E96" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F96" t="s">
         <v>218</v>
@@ -6669,7 +6681,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>10.47821640968323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6686,7 +6698,7 @@
         <v>215</v>
       </c>
       <c r="E97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F97" t="s">
         <v>215</v>
@@ -6698,7 +6710,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>5.898989677429199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6715,7 +6727,7 @@
         <v>215</v>
       </c>
       <c r="E98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F98" t="s">
         <v>215</v>
@@ -6727,7 +6739,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>7.05492115020752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6744,7 +6756,7 @@
         <v>217</v>
       </c>
       <c r="E99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F99" t="s">
         <v>215</v>
@@ -6756,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>8.662250518798828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6773,7 +6785,7 @@
         <v>218</v>
       </c>
       <c r="E100" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F100" t="s">
         <v>215</v>
@@ -6785,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>17.59978342056274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6802,7 +6814,7 @@
         <v>216</v>
       </c>
       <c r="E101" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F101" t="s">
         <v>217</v>
@@ -6814,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>9.60565972328186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6843,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>11.70490217208862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6872,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>17.35566806793213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6889,7 +6901,7 @@
         <v>218</v>
       </c>
       <c r="E104" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F104" t="s">
         <v>217</v>
@@ -6901,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>5.626947641372681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6918,7 +6930,7 @@
         <v>217</v>
       </c>
       <c r="E105" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F105" t="s">
         <v>215</v>
@@ -6930,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>4.637882709503174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6947,7 +6959,7 @@
         <v>218</v>
       </c>
       <c r="E106" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F106" t="s">
         <v>218</v>
@@ -6959,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>4.132702827453613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6976,7 +6988,7 @@
         <v>216</v>
       </c>
       <c r="E107" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F107" t="s">
         <v>216</v>
@@ -6988,7 +7000,7 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>5.923847198486328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -7017,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>6.169837236404419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -7034,7 +7046,7 @@
         <v>217</v>
       </c>
       <c r="E109" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F109" t="s">
         <v>217</v>
@@ -7046,7 +7058,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>7.377456426620483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -7063,7 +7075,7 @@
         <v>216</v>
       </c>
       <c r="E110" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F110" t="s">
         <v>217</v>
@@ -7075,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>9.536341190338135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -7092,7 +7104,7 @@
         <v>218</v>
       </c>
       <c r="E111" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F111" t="s">
         <v>218</v>
@@ -7104,7 +7116,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>3.745950937271118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -7133,7 +7145,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>10.38366961479187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -7162,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="I113">
-        <v>7.799799919128418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7179,7 +7191,7 @@
         <v>216</v>
       </c>
       <c r="E114" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F114" t="s">
         <v>218</v>
@@ -7191,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>6.65986442565918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7208,7 +7220,7 @@
         <v>217</v>
       </c>
       <c r="E115" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F115" t="s">
         <v>217</v>
@@ -7220,7 +7232,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>6.928957223892212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7249,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>9.754759311676025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7266,7 +7278,7 @@
         <v>217</v>
       </c>
       <c r="E117" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F117" t="s">
         <v>217</v>
@@ -7278,7 +7290,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>6.535137414932251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7295,7 +7307,7 @@
         <v>216</v>
       </c>
       <c r="E118" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F118" t="s">
         <v>216</v>
@@ -7307,7 +7319,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>4.031529664993286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7336,7 +7348,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>12.79963421821594</v>
+        <v>23.42080545425415</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7353,7 +7365,7 @@
         <v>215</v>
       </c>
       <c r="E120" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F120" t="s">
         <v>216</v>
@@ -7365,7 +7377,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>10.12636375427246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7382,7 +7394,7 @@
         <v>217</v>
       </c>
       <c r="E121" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F121" t="s">
         <v>218</v>
@@ -7394,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>7.749805450439453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7411,7 +7423,7 @@
         <v>217</v>
       </c>
       <c r="E122" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F122" t="s">
         <v>216</v>
@@ -7423,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>4.774926424026489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7440,7 +7452,7 @@
         <v>218</v>
       </c>
       <c r="E123" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F123" t="s">
         <v>217</v>
@@ -7452,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>6.928311586380005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7481,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>15.91883420944214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7510,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>13.40069890022278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7527,7 +7539,7 @@
         <v>218</v>
       </c>
       <c r="E126" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F126" t="s">
         <v>216</v>
@@ -7539,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>9.307230949401855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7568,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="I127">
-        <v>25.43976545333862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7597,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>8.521291732788086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7614,7 +7626,7 @@
         <v>215</v>
       </c>
       <c r="E129" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F129" t="s">
         <v>217</v>
@@ -7626,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>18.88103055953979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7643,7 +7655,7 @@
         <v>216</v>
       </c>
       <c r="E130" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F130" t="s">
         <v>215</v>
@@ -7655,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>7.249335765838623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7672,7 +7684,7 @@
         <v>215</v>
       </c>
       <c r="E131" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F131" t="s">
         <v>216</v>
@@ -7684,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>8.561111450195312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7713,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>10.38455247879028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7742,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>10.4170868396759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7771,7 +7783,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>71.55719995498657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7788,7 +7800,7 @@
         <v>217</v>
       </c>
       <c r="E135" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F135" t="s">
         <v>216</v>
@@ -7800,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>8.840463638305664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7829,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="I136">
-        <v>9.482836246490479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7846,7 +7858,7 @@
         <v>216</v>
       </c>
       <c r="E137" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F137" t="s">
         <v>216</v>
@@ -7858,7 +7870,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>9.350675106048584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7887,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>16.93280816078186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7916,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="I139">
-        <v>9.407369613647461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -7945,7 +7957,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>7.887656211853027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -7974,7 +7986,7 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>10.08683943748474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -7991,7 +8003,7 @@
         <v>218</v>
       </c>
       <c r="E142" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F142" t="s">
         <v>216</v>
@@ -8003,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>4.817961931228638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -8032,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>9.819543123245239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -8049,7 +8061,7 @@
         <v>217</v>
       </c>
       <c r="E144" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F144" t="s">
         <v>217</v>
@@ -8061,7 +8073,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>8.394229412078857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -8090,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="I145">
-        <v>19.40051865577698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -8119,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>10.18268513679504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -8136,7 +8148,7 @@
         <v>217</v>
       </c>
       <c r="E147" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F147" t="s">
         <v>217</v>
@@ -8148,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>7.446593999862671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8165,7 +8177,7 @@
         <v>215</v>
       </c>
       <c r="E148" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F148" t="s">
         <v>215</v>
@@ -8177,7 +8189,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>7.37327241897583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8206,7 +8218,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>19.1503849029541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -8223,7 +8235,7 @@
         <v>216</v>
       </c>
       <c r="E150" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G150" t="s">
         <v>216</v>
@@ -8232,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>3.269365310668945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -8249,7 +8261,7 @@
         <v>215</v>
       </c>
       <c r="E151" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F151" t="s">
         <v>217</v>
@@ -8261,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>5.951877355575562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -8278,7 +8290,7 @@
         <v>215</v>
       </c>
       <c r="E152" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F152" t="s">
         <v>218</v>
@@ -8290,7 +8302,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>9.559409856796265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -8307,7 +8319,7 @@
         <v>218</v>
       </c>
       <c r="E153" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F153" t="s">
         <v>218</v>
@@ -8319,7 +8331,7 @@
         <v>1</v>
       </c>
       <c r="I153">
-        <v>8.02877140045166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -8348,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>18.40381407737732</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -8365,7 +8377,7 @@
         <v>218</v>
       </c>
       <c r="E155" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F155" t="s">
         <v>217</v>
@@ -8377,7 +8389,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>6.594960689544678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -8406,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>5.806511402130127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -8435,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <v>21.05902433395386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8452,10 +8464,10 @@
         <v>215</v>
       </c>
       <c r="E158" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F158" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G158" t="s">
         <v>215</v>
@@ -8464,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <v>8.969438552856445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8493,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <v>14.26143622398376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8522,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>13.78131484985352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8551,7 +8563,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>17.62827515602112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8580,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <v>19.00441479682922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -8597,7 +8609,7 @@
         <v>215</v>
       </c>
       <c r="E163" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F163" t="s">
         <v>215</v>
@@ -8609,7 +8621,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>9.024282455444336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -8638,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <v>19.78279328346252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -8655,7 +8667,7 @@
         <v>217</v>
       </c>
       <c r="E165" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F165" t="s">
         <v>215</v>
@@ -8667,7 +8679,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>7.083478927612305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -8696,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <v>13.65191078186035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -8713,7 +8725,7 @@
         <v>218</v>
       </c>
       <c r="E167" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F167" t="s">
         <v>217</v>
@@ -8725,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>13.42405819892883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -8742,7 +8754,7 @@
         <v>217</v>
       </c>
       <c r="E168" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F168" t="s">
         <v>217</v>
@@ -8754,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>7.956650972366333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -8771,7 +8783,7 @@
         <v>218</v>
       </c>
       <c r="E169" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F169" t="s">
         <v>216</v>
@@ -8783,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="I169">
-        <v>7.310682058334351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -8800,7 +8812,7 @@
         <v>218</v>
       </c>
       <c r="E170" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F170" t="s">
         <v>218</v>
@@ -8812,7 +8824,7 @@
         <v>1</v>
       </c>
       <c r="I170">
-        <v>11.00744342803955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -8829,7 +8841,7 @@
         <v>217</v>
       </c>
       <c r="E171" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F171" t="s">
         <v>217</v>
@@ -8841,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="I171">
-        <v>7.808735847473145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -8858,7 +8870,7 @@
         <v>216</v>
       </c>
       <c r="E172" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F172" t="s">
         <v>216</v>
@@ -8870,7 +8882,7 @@
         <v>1</v>
       </c>
       <c r="I172">
-        <v>7.160088300704956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -8887,7 +8899,7 @@
         <v>217</v>
       </c>
       <c r="E173" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F173" t="s">
         <v>218</v>
@@ -8899,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>6.805642127990723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -8916,7 +8928,7 @@
         <v>216</v>
       </c>
       <c r="E174" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F174" t="s">
         <v>215</v>
@@ -8928,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>11.28956460952759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -8945,10 +8957,10 @@
         <v>216</v>
       </c>
       <c r="E175" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F175" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G175" t="s">
         <v>216</v>
@@ -8957,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="I175">
-        <v>8.369704008102417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -8974,7 +8986,7 @@
         <v>216</v>
       </c>
       <c r="E176" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F176" t="s">
         <v>217</v>
@@ -8986,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>5.754163503646851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -9003,7 +9015,7 @@
         <v>217</v>
       </c>
       <c r="E177" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F177" t="s">
         <v>217</v>
@@ -9015,7 +9027,7 @@
         <v>1</v>
       </c>
       <c r="I177">
-        <v>8.185333251953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -9044,7 +9056,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>19.37206745147705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -9073,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>15.52282190322876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -9102,7 +9114,7 @@
         <v>0</v>
       </c>
       <c r="I180">
-        <v>9.913131713867188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -9119,7 +9131,7 @@
         <v>217</v>
       </c>
       <c r="E181" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F181" t="s">
         <v>217</v>
@@ -9131,7 +9143,7 @@
         <v>1</v>
       </c>
       <c r="I181">
-        <v>13.34150338172913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -9148,7 +9160,7 @@
         <v>217</v>
       </c>
       <c r="E182" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F182" t="s">
         <v>217</v>
@@ -9160,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="I182">
-        <v>6.598680257797241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -9177,7 +9189,7 @@
         <v>215</v>
       </c>
       <c r="E183" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F183" t="s">
         <v>217</v>
@@ -9189,7 +9201,7 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>8.739238500595093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -9218,7 +9230,7 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>16.06912064552307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -9235,7 +9247,7 @@
         <v>215</v>
       </c>
       <c r="E185" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F185" t="s">
         <v>217</v>
@@ -9247,7 +9259,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>7.811636924743652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -9264,7 +9276,7 @@
         <v>218</v>
       </c>
       <c r="E186" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F186" t="s">
         <v>217</v>
@@ -9276,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>9.292179822921753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -9305,7 +9317,7 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>20.1910297870636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -9322,7 +9334,7 @@
         <v>218</v>
       </c>
       <c r="E188" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F188" t="s">
         <v>218</v>
@@ -9334,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="I188">
-        <v>9.135830640792847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -9351,7 +9363,7 @@
         <v>216</v>
       </c>
       <c r="E189" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F189" t="s">
         <v>218</v>
@@ -9363,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>10.40115714073181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -9380,7 +9392,7 @@
         <v>216</v>
       </c>
       <c r="E190" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F190" t="s">
         <v>216</v>
@@ -9392,7 +9404,7 @@
         <v>1</v>
       </c>
       <c r="I190">
-        <v>10.20389819145203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -9409,7 +9421,7 @@
         <v>216</v>
       </c>
       <c r="E191" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F191" t="s">
         <v>218</v>
@@ -9421,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>12.19255423545837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -9438,7 +9450,7 @@
         <v>218</v>
       </c>
       <c r="E192" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F192" t="s">
         <v>215</v>
@@ -9450,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>6.442182302474976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -9467,7 +9479,7 @@
         <v>215</v>
       </c>
       <c r="E193" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F193" t="s">
         <v>217</v>
@@ -9479,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>5.441311359405518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -9496,7 +9508,7 @@
         <v>217</v>
       </c>
       <c r="E194" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F194" t="s">
         <v>215</v>
@@ -9508,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>12.79683637619019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -9525,7 +9537,7 @@
         <v>215</v>
       </c>
       <c r="E195" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F195" t="s">
         <v>215</v>
@@ -9537,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="I195">
-        <v>6.512320280075073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -9554,7 +9566,7 @@
         <v>215</v>
       </c>
       <c r="E196" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F196" t="s">
         <v>216</v>
@@ -9566,7 +9578,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>9.786411285400391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -9583,7 +9595,7 @@
         <v>217</v>
       </c>
       <c r="E197" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F197" t="s">
         <v>218</v>
@@ -9595,7 +9607,7 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>16.71649026870728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -9612,7 +9624,7 @@
         <v>216</v>
       </c>
       <c r="E198" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F198" t="s">
         <v>216</v>
@@ -9624,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="I198">
-        <v>8.340067625045776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -9641,10 +9653,10 @@
         <v>218</v>
       </c>
       <c r="E199" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F199" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G199" t="s">
         <v>218</v>
@@ -9653,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="I199">
-        <v>9.466916561126709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -9670,7 +9682,7 @@
         <v>216</v>
       </c>
       <c r="E200" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F200" t="s">
         <v>216</v>
@@ -9682,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="I200">
-        <v>5.862993955612183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -9699,7 +9711,7 @@
         <v>218</v>
       </c>
       <c r="E201" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F201" t="s">
         <v>218</v>
@@ -9711,7 +9723,7 @@
         <v>1</v>
       </c>
       <c r="I201">
-        <v>16.42301201820374</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
